--- a/review/abilities/workbooks/12_Ancestry_Halfling.xlsx
+++ b/review/abilities/workbooks/12_Ancestry_Halfling.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Traits" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Pairs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Compare" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Change Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traits" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pairs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compare" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Traits'!$A$4:$L$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Traits'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pairs'!$A$4:$G$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Pairs'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Change Log'!$A$4:$R$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Change Log'!$A$4:$Q$204</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Change Log'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Change Log'!$A$1:$R$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Change Log'!$A$1:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -188,7 +188,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -225,19 +225,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <color rgb="001F3864"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D9E1F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -730,7 +717,7 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Small, lucky and social. Halfling has HP +1, Speed 5, and traits for luck, quiet movement, shared meals, small openings and fear resistance. The ancestry is built for infiltration and support rather than raw combat.</t>
+          <t>Small, lucky and social. Halfling is Size Small with HP +1, Speed 5, and traits for luck, quick talk, endless pockets, hiding behind larger creatures and fear resistance. The ancestry is built for infiltration and support rather than raw combat.</t>
         </is>
       </c>
     </row>
@@ -744,7 +731,7 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>A Little Luck is the broadest trait in the game; Under Their Noses is a strong infiltration tool; Quiet as a Burrow has a nice team beat. The ancestry has a clear cultural voice.</t>
+          <t>A Little Luck is the broadest trait in the game; Under Their Noses is a strong infiltration tool; Quick Tongue is a strong social tool. The ancestry has a clear cultural voice.</t>
         </is>
       </c>
     </row>
@@ -758,7 +745,7 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>No trait raises HP or Speed, and base HP/Speed are the lowest. Second Breakfast is mechanically thin. Bigger on the Inside is niche unless fear is common. Halfling is the only ancestry with no stat trait.</t>
+          <t>Base HP/Speed are the lowest. Bigger on the Inside now covers HP, but the ancestry still has no Speed trait. Endless Pockets is a small utility benefit.</t>
         </is>
       </c>
     </row>
@@ -772,7 +759,7 @@
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Add +1 maximum HP to Bigger on the Inside or Second Breakfast to close the stat gap. Monitor A Little Luck; if it dominates, limit it to non-attack rolls or once per scene. Add a concrete example to Under Their Noses.</t>
+          <t>Bigger on the Inside now closes the HP gap. Monitor A Little Luck; if it dominates, limit it to non-attack rolls or once per scene. Monitor Quick Tongue alongside A Little Luck in social-heavy campaigns.</t>
         </is>
       </c>
     </row>
@@ -818,7 +805,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock</t>
+          <t>Hard as Bedrock</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -867,7 +854,7 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Combat, Defense, Exploration, Social, Support, Utility</t>
+          <t>Combat, Defense, Exploration, Social, Utility</t>
         </is>
       </c>
     </row>
@@ -884,12 +871,12 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Never Quite Finished, Road in the Blood</t>
+          <t>Never Quite Finished</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Defense, Exploration, Movement, Social, Support, Utility</t>
+          <t>Defense, Exploration, Social, Utility</t>
         </is>
       </c>
     </row>
@@ -935,12 +922,12 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Halfling is HP +1 and Speed 5 with no trait that raises HP or Speed. Dwarf can reach HP +5, Human HP +3 or Speed 7, Elf Speed 7. Halfling's traits are mostly situational except A Little Luck.</t>
+          <t>Halfling is HP +1 and Speed 5. Bigger on the Inside now raises HP, but no Halfling trait raises Speed, and the ancestry still has the lowest base HP/Speed.</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Add +1 maximum HP to Bigger on the Inside or Second Breakfast, or give Under Their Noses a broader always-on benefit. If the gap is intentional, state the compensation (luck/stealth) in the ancestry text.</t>
+          <t>Keep the +1 HP on Bigger on the Inside. Consider a Speed trait or a small always-on movement benefit if Halfling still feels slow. If the gap is intentional, state the luck/stealth compensation in the ancestry text.</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1176,12 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>1 Boon to rolls affected by Frightened; resolve Boons and Banes normally; not immune to fear.</t>
+          <t>1 Boon to rolls affected by Frightened and +1 maximum HP; resolve Boons and Banes normally.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Gain 1 Boon to rolls affected by Frightened. Resolve the Boon and Banes normally; you are not immune to fear.</t>
+          <t>Gain 1 Boon to rolls affected by Frightened. Your maximum HP increases by 1. Resolve the Boon and Banes normally.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -1209,12 +1196,12 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Good fear resistance with a great name. It is niche unless the campaign features fear.</t>
+          <t>Fear resistance plus +1 maximum HP. It is now the Halfling durability trait, not only a niche fear pick.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Add +1 maximum HP to make it the Halfling durability trait and fix the ancestry stat gap. Keep the fear Boon.</t>
+          <t>Approved: added +1 maximum HP; keep the fear Boon.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr"/>
@@ -1241,12 +1228,12 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Fit through openings the DA judges suitable for your actual small size; 1 Boon to hiding behind ordinary furniture that plausibly conceals you. Standing creatures still block their squares.</t>
+          <t>Gain 1 Boon to hiding. When adjacent to a standing creature at least one size larger, you can hide behind it even in combat and without other cover.</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>You fit through openings the DA judges suitable for your actual small size, and gain 1 Boon to hiding behind ordinary furniture that plausibly conceals you. Standing creatures still block their squares; no free movement through enemies.</t>
+          <t>You gain 1 Boon to hiding. When you are adjacent to a standing creature at least one size larger than you, you can attempt to hide behind it, even in combat and with no other cover, as long as it is between you and the observer. The creature can be an ally or an enemy.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1261,12 +1248,12 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Strong infiltration trait with two useful clauses. The size judgement is intentionally flexible but can vary by table.</t>
+          <t>Always-on hiding Boon plus a size-based cover exception. Strong for a Small Halfling in melee, and no longer limited to furniture.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Give one concrete example of a suitable opening (barred window, drain, gap under a stall) and clarify whether squeezing costs movement.</t>
+          <t>Approved: unconditional hiding Boon and larger-creature cover clause. Halfling is Size Small.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr"/>
@@ -1283,7 +1270,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Quiet as a Burrow</t>
+          <t>Quick Tongue</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -1293,17 +1280,17 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1 Boon to quiet movement outside combat. On a Strong result, one companion following your route gains 1 Boon to their next quiet-movement roll this scene.</t>
+          <t>1 Boon to Guile rolls to negotiate or argue; 2 Boons when using Guile to defend your own or an ally’s actions.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Gain 1 Boon to quiet movement outside combat. On a Strong result, one willing companion following your route gains 1 Boon to their next quiet-movement roll this scene. You cannot confer Hidden by walking in open view.</t>
+          <t>Gain 1 Boon to Guile rolls to negotiate or argue. When you use Guile to defend your own or an ally’s actions, gain 2 Boons instead.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Exploration, Utility</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -1313,12 +1300,12 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Good stealth trait with a nice team beat. It is explicitly outside combat, which keeps it from overshadowing combat stealth.</t>
+          <t>Strong social/verbal trait: broad negotiation and argument Boon, stronger when defending your own or an ally’s actions. Fits Halfling confidence.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Clarify what 'quiet movement' covers (Stealth rolls, avoiding notice, not all movement) and whether the companion must stay on your route.</t>
+          <t>Approved: replaced Quiet as a Burrow with Quick Tongue; 1 Boon to negotiate/argue, 2 Boons to defend actions.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr"/>
@@ -1329,7 +1316,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1">
+    <row r="8" ht="41.5" customHeight="1">
       <c r="A8" s="8" t="n">
         <v>4</v>
       </c>
@@ -1345,12 +1332,12 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Once per day, before a roll that uses an attribute, gain 1 Boon. No reroll after seeing the result; no effect on inventory dice.</t>
+          <t>Once per day, before a roll that uses an attribute, gain 3 Boons. Describe a small piece of good fortune.</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Once per day, before a roll that uses an attribute, gain 1 Boon. Describe a small piece of good fortune. No reroll after seeing the result and no effect on inventory dice.</t>
+          <t>Once per day, before a roll that uses an attribute, gain 3 Boons. Describe a small piece of good fortune.</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -1365,12 +1352,12 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>The broadest ancestry trait in the game: it can apply to attacks, defenses and any skill. It is likely the Halfling default.</t>
+          <t>Once-per-day +3 Boons is a spotlight moment at the system cap. Broad, impactful and still limited to one declared roll per day.</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Monitor. If it dominates, make it once per scene, require a roll with a meaningful consequence, or limit it to non-attack rolls. Keep it if the Halfling stat gap is intentional.</t>
+          <t>Approved: once per day, gain 3 Boons on any attribute roll. It is intentionally impactful; monitor if it dominates a session.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr"/>
@@ -1381,13 +1368,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
+    <row r="9" ht="29" customHeight="1">
       <c r="A9" s="7" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Second Breakfast</t>
+          <t>Endless Pockets</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -1397,17 +1384,17 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>When sharing a food bundle with one companion during a safe meal, make one inventory check for the two of you instead of one each.</t>
+          <t>Your Bulk capacity increases by 1.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>When sharing a food bundle with one companion during a safe meal, make one inventory check for the two of you instead of one each. Food is still required; this grants no healing, resistance or extra recovery.</t>
+          <t>Your Bulk capacity increases by 1.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Support, Utility</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -1417,12 +1404,12 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Charming and very Halfling, but mechanically thin: it saves one inventory check and requires a safe meal.</t>
+          <t>Simple inventory trait: +1 Bulk capacity. The pockets-with-pockets flavor carries it.</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Tie it to the Halfling durability theme: add +1 maximum HP, or let the shared meal restore 1 additional HP / grant a small morale Boon. Keep the food requirement.</t>
+          <t>Approved: replaced Second Breakfast with Endless Pockets; +1 Bulk capacity.</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr"/>
@@ -1450,15 +1437,12 @@
       <formula>J5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>J5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>J5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="J5:J9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1578,22 +1562,22 @@
     <row r="6" ht="41.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Bigger on the Inside + Quiet as a Burrow</t>
+          <t>Bigger on the Inside + Quick Tongue</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Defense, Exploration, Utility</t>
+          <t>Defense, Social</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Durable scout</t>
+          <t>Flexible adventurer</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Bigger on the Inside leans defense; Quiet as a Burrow leans exploration, utility. Together they cover defense, exploration, utility.</t>
+          <t>Bigger on the Inside leans defense; Quick Tongue leans social. Together they cover defense, social.</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -1636,22 +1620,22 @@
     <row r="8" ht="41.5" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Bigger on the Inside + Second Breakfast</t>
+          <t>Bigger on the Inside + Endless Pockets</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Defense, Support, Utility</t>
+          <t>Defense, Utility</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Protective support</t>
+          <t>Practical fighter</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Bigger on the Inside leans defense; Second Breakfast leans support, utility. Together they cover defense, support, utility.</t>
+          <t>Bigger on the Inside leans defense; Endless Pockets leans utility. Together they cover defense, utility.</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -1665,22 +1649,22 @@
     <row r="9" ht="41.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Under Their Noses + Quiet as a Burrow</t>
+          <t>Under Their Noses + Quick Tongue</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Exploration, Utility</t>
+          <t>Exploration, Social, Utility</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Skill specialist</t>
+          <t>Guide and envoy</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Under Their Noses leans exploration, utility; Quiet as a Burrow leans exploration, utility. Together they cover exploration, utility.</t>
+          <t>Under Their Noses leans exploration, utility; Quick Tongue leans social. Together they cover exploration, social, utility.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -1723,22 +1707,22 @@
     <row r="11" ht="41.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Under Their Noses + Second Breakfast</t>
+          <t>Under Their Noses + Endless Pockets</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Exploration, Support, Utility</t>
+          <t>Exploration, Utility</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Camp keeper</t>
+          <t>Skill specialist</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Under Their Noses leans exploration, utility; Second Breakfast leans support, utility. Together they cover exploration, support, utility.</t>
+          <t>Under Their Noses leans exploration, utility; Endless Pockets leans utility. Together they cover exploration, utility.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -1752,12 +1736,12 @@
     <row r="12" ht="41.5" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Quiet as a Burrow + A Little Luck</t>
+          <t>Quick Tongue + A Little Luck</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Combat, Defense, Exploration, Social, Utility</t>
+          <t>Combat, Defense, Social, Utility</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1767,7 +1751,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Quiet as a Burrow leans exploration, utility; A Little Luck leans combat, defense, utility, social. Together they cover combat, defense, exploration, social, utility.</t>
+          <t>Quick Tongue leans social; A Little Luck leans combat, defense, utility, social. Together they cover combat, defense, social, utility.</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1781,22 +1765,22 @@
     <row r="13" ht="41.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Quiet as a Burrow + Second Breakfast</t>
+          <t>Quick Tongue + Endless Pockets</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Exploration, Support, Utility</t>
+          <t>Social, Utility</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Camp keeper</t>
+          <t>Skill specialist</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Quiet as a Burrow leans exploration, utility; Second Breakfast leans support, utility. Together they cover exploration, support, utility.</t>
+          <t>Quick Tongue leans social; Endless Pockets leans utility. Together they cover social, utility.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -1810,12 +1794,12 @@
     <row r="14" ht="41.5" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>A Little Luck + Second Breakfast</t>
+          <t>A Little Luck + Endless Pockets</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Combat, Defense, Social, Support, Utility</t>
+          <t>Combat, Defense, Social, Utility</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1825,7 +1809,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>A Little Luck leans combat, defense, utility, social; Second Breakfast leans support, utility. Together they cover combat, defense, social, support, utility.</t>
+          <t>A Little Luck leans combat, defense, utility, social; Endless Pockets leans utility. Together they cover combat, defense, social, utility.</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -1853,15 +1837,12 @@
       <formula>F5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>F5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>F5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="F5:F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1978,7 +1959,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock</t>
+          <t>Hard as Bedrock</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -2067,7 +2048,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Combat, Defense, Exploration, Social, Support, Utility</t>
+          <t>Combat, Defense, Exploration, Social, Utility</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -2104,12 +2085,12 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Never Quite Finished, Road in the Blood</t>
+          <t>Never Quite Finished</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Defense, Exploration, Movement, Social, Support, Utility</t>
+          <t>Defense, Exploration, Social, Utility</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -2140,7 +2121,7 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>• Stubborn as Bedrock and Never Quite Finished are both '+1 maximum HP'; Grace of the Elder Folk and Road in the Blood are both '+1 base Speed'. The mechanics are identical; only the fiction differs (F12).</t>
+          <t>• Hard as Bedrock and Never Quite Finished are both '+1 maximum HP'; Grace of the Elder Folk and Road in the Blood are both '+1 base Speed'. The mechanics are identical; only the fiction differs (F12).</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2204,12 +2185,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" style="11" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" style="11" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2290,30 +2270,25 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Playtest status</t>
+          <t>Book issue</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>Book issue</t>
+          <t>Foundry issue</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Foundry issue</t>
+          <t>Commit SHA</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Commit SHA</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2337,7 +2312,6 @@
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="7" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr"/>
@@ -2357,7 +2331,6 @@
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr"/>
@@ -2377,7 +2350,6 @@
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="8" t="inlineStr"/>
@@ -2397,7 +2369,6 @@
       <c r="O8" s="8" t="inlineStr"/>
       <c r="P8" s="8" t="inlineStr"/>
       <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr"/>
@@ -2417,7 +2388,6 @@
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="8" t="inlineStr"/>
@@ -2437,7 +2407,6 @@
       <c r="O10" s="8" t="inlineStr"/>
       <c r="P10" s="8" t="inlineStr"/>
       <c r="Q10" s="8" t="inlineStr"/>
-      <c r="R10" s="8" t="inlineStr"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr"/>
@@ -2457,7 +2426,6 @@
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="7" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="8" t="inlineStr"/>
@@ -2477,7 +2445,6 @@
       <c r="O12" s="8" t="inlineStr"/>
       <c r="P12" s="8" t="inlineStr"/>
       <c r="Q12" s="8" t="inlineStr"/>
-      <c r="R12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr"/>
@@ -2497,7 +2464,6 @@
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="7" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="8" t="inlineStr"/>
@@ -2517,7 +2483,6 @@
       <c r="O14" s="8" t="inlineStr"/>
       <c r="P14" s="8" t="inlineStr"/>
       <c r="Q14" s="8" t="inlineStr"/>
-      <c r="R14" s="8" t="inlineStr"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr"/>
@@ -2537,7 +2502,6 @@
       <c r="O15" s="7" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="7" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="8" t="inlineStr"/>
@@ -2557,23 +2521,19 @@
       <c r="O16" s="8" t="inlineStr"/>
       <c r="P16" s="8" t="inlineStr"/>
       <c r="Q16" s="8" t="inlineStr"/>
-      <c r="R16" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R204"/>
+  <autoFilter ref="A4:Q204"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation sqref="I5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Change type" error="Choose one of: Editorial, Wording, Mechanical, Rename, Add, Remove, Tier / DP, ID migration" promptTitle="Change type" prompt="Classify the change." type="list">
       <formula1>"Editorial,Wording,Mechanical,Rename,Add,Remove,Tier / DP,ID migration"</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose one of: Proposed, Approved, Rejected, Deferred" promptTitle="Decision" prompt="Approval state for this change." type="list">
       <formula1>"Proposed,Approved,Rejected,Deferred"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M5:M204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Playtest status" error="Choose one of: Not needed, Pending, Passed, Failed, N/A" promptTitle="Playtest status" prompt="Playtest evidence for mechanical changes." type="list">
-      <formula1>"Not needed,Pending,Passed,Failed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
